--- a/Base/Backlog_21.xlsx
+++ b/Base/Backlog_21.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\Base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BC3E1E0-9798-4DB0-A88E-8CF1414680C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE479DD1-C280-41EB-BD7C-4B4D9EDEBB17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="418" activeTab="1" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="418" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="2" r:id="rId1"/>
@@ -115,9 +115,6 @@
     <t>Eduardo da Silva</t>
   </si>
   <si>
-    <t>Felipe do Nascimento</t>
-  </si>
-  <si>
     <t>Jose Acevedo</t>
   </si>
   <si>
@@ -125,6 +122,9 @@
   </si>
   <si>
     <t>Higor Cruz</t>
+  </si>
+  <si>
+    <t>Felipe Nascimento</t>
   </si>
 </sst>
 </file>
@@ -750,7 +750,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C5" s="9">
         <v>2025</v>
@@ -774,7 +774,7 @@
         <v>45803</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>11</v>
@@ -809,7 +809,7 @@
         <v>45803</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K6" s="9" t="s">
         <v>11</v>
@@ -844,7 +844,7 @@
         <v>45803</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K7" s="9" t="s">
         <v>11</v>
@@ -984,7 +984,7 @@
         <v>45803</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K11" s="9" t="s">
         <v>11</v>
@@ -1019,7 +1019,7 @@
         <v>45803</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K12" s="9" t="s">
         <v>11</v>
@@ -1030,7 +1030,7 @@
         <v>4</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C13" s="9">
         <v>2025</v>
@@ -1054,7 +1054,7 @@
         <v>45803</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K13" s="9" t="s">
         <v>11</v>
@@ -1065,7 +1065,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C14" s="9">
         <v>2025</v>
@@ -1100,7 +1100,7 @@
         <v>4</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C15" s="9">
         <v>2025</v>
@@ -1159,7 +1159,7 @@
         <v>45803</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K16" s="9" t="s">
         <v>11</v>
@@ -1704,7 +1704,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C2" s="9">
         <v>2025</v>
@@ -1728,7 +1728,7 @@
         <v>45803</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K2" s="9" t="s">
         <v>15</v>
@@ -1739,7 +1739,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3" s="9">
         <v>2025</v>
@@ -1763,7 +1763,7 @@
         <v>45803</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>15</v>
@@ -1774,7 +1774,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C4" s="9">
         <v>2025</v>
@@ -1798,7 +1798,7 @@
         <v>45803</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K4" s="9" t="s">
         <v>15</v>
